--- a/sources/yoshimitsu_step8b.xlsx
+++ b/sources/yoshimitsu_step8b.xlsx
@@ -7506,12 +7506,12 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>ms[!]</t>
+          <t>ms!</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>[!]h</t>
+          <t>!h</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>[!]m</t>
+          <t>!m</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
@@ -11014,12 +11014,12 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>[!]-[!]</t>
+          <t>!-!</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">

--- a/sources/yoshimitsu_step8b.xlsx
+++ b/sources/yoshimitsu_step8b.xlsx
@@ -857,6 +857,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -919,6 +924,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -979,6 +989,11 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -11694,6 +11709,11 @@
           <t>hmmhhLm!!!</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -11741,6 +11761,11 @@
           <t>hmmhmmmm!!</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -11788,6 +11813,11 @@
           <t>hhmhhLm!!!</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -11835,6 +11865,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -11882,6 +11917,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -11929,6 +11969,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -11974,6 +12019,11 @@
       <c r="T140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
